--- a/r5-aist-trustworthyai-main/StructureDefinition-patient-ai-info-provided.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-patient-ai-info-provided.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
